--- a/ToyStory-2025-ChatGPT.xlsx
+++ b/ToyStory-2025-ChatGPT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Extreme SSD/Download-SSD/DL26-03-Mar/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kcc29/dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E5BE57-F869-7045-AD00-583A6F2D90D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639C13A8-95E6-8E43-8B6E-94BE71B4481D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16420" yWindow="6000" windowWidth="32480" windowHeight="21000" xr2:uid="{548542D2-0B7B-1345-B431-5F02961271F3}"/>
+    <workbookView xWindow="820" yWindow="600" windowWidth="32480" windowHeight="21000" xr2:uid="{548542D2-0B7B-1345-B431-5F02961271F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -176,9 +176,6 @@
     <t>https://cf.shopee.co.th/file/f6c557cda4de3d3b494cc9c95c101f74</t>
   </si>
   <si>
-    <t>https://drive.google.com/thumbnail?id=1leUODukML9SLqMv0ocqaHWpgWz6n88eb&amp;sz=w740</t>
-  </si>
-  <si>
     <t>Total_Sales_Baht</t>
   </si>
   <si>
@@ -192,13 +189,16 @@
   </si>
   <si>
     <t>sales_Channel</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dv4ez0qwp/image/upload/v1772800035/SheetDLC068_ToyStory_k4xrw9.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -224,6 +224,14 @@
       <color theme="1"/>
       <name val="Helvetica"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -281,10 +289,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -293,8 +302,10 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -644,19 +655,19 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -668,7 +679,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -1160,8 +1171,8 @@
       <c r="H18" t="s">
         <v>27</v>
       </c>
-      <c r="I18" t="s">
-        <v>45</v>
+      <c r="I18" s="8" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
@@ -1653,8 +1664,8 @@
       <c r="H35" t="s">
         <v>27</v>
       </c>
-      <c r="I35" t="s">
-        <v>45</v>
+      <c r="I35" s="8" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
@@ -2146,8 +2157,8 @@
       <c r="H52" t="s">
         <v>27</v>
       </c>
-      <c r="I52" t="s">
-        <v>45</v>
+      <c r="I52" s="8" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
@@ -2639,8 +2650,8 @@
       <c r="H69" t="s">
         <v>27</v>
       </c>
-      <c r="I69" t="s">
-        <v>45</v>
+      <c r="I69" s="8" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2649,6 +2660,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="I69" r:id="rId1" xr:uid="{85CFFB39-F392-3444-AB46-F5113632353E}"/>
+    <hyperlink ref="I52" r:id="rId2" xr:uid="{357860F6-F73F-9D42-AC09-1A02382FE3C2}"/>
+    <hyperlink ref="I35" r:id="rId3" xr:uid="{28ED4087-1C6E-0E44-A269-6DCA073E79C6}"/>
+    <hyperlink ref="I18" r:id="rId4" xr:uid="{AECEFEE0-2315-AC45-BE22-701C9182B321}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
